--- a/artfynd/A 48875-2022 artfynd.xlsx
+++ b/artfynd/A 48875-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48875-2022 artfynd.xlsx
+++ b/artfynd/A 48875-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,137 +1136,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>90537402</v>
-      </c>
-      <c r="B6" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>219955</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Slåttergubbe</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Arnica montana</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Slätetorp, söder om, Nrk</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>510276.2152971127</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6535710.061514929</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Askersund</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Lerbäck</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>T-Ask-8048</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>1985-06-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>1985-06-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Hagartad skogskant</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Henrik Josefsson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Gunnar Hallin</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
